--- a/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/hxassetliabilitystatement/HXAssetLiabilityStatement.xlsx
+++ b/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/hxassetliabilitystatement/HXAssetLiabilityStatement.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20373"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C1744B1-D04F-4EBB-87B6-D303FC261425}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3648068D-4EED-475E-9623-F02E9CC3986A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,14 +292,6 @@
     <t>${entity.qmBal.undisProfit}</t>
   </si>
   <si>
-    <t>${entity.assetTotalQC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>${entity.assetTotalQM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>${entity.liabilityTotalQC}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -329,6 +321,14 @@
   </si>
   <si>
     <t>${entity.liabilityTotalQM}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${entity.assetTotalQC}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${entity.assetTotalQM}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1238,10 +1238,10 @@
         <v>12</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -1274,7 +1274,7 @@
         <v>14</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>80</v>
@@ -1304,16 +1304,16 @@
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F20" s="11">
         <v>16</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -1365,10 +1365,10 @@
         <v>20</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>24</v>
@@ -1377,10 +1377,10 @@
         <v>20</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.15">
